--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126946023</v>
       </c>
       <c r="B2" t="n">
-        <v>42992</v>
+        <v>42996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126946023</v>
       </c>
       <c r="B2" t="n">
-        <v>42996</v>
+        <v>42998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126946023</v>
       </c>
       <c r="B2" t="n">
-        <v>42998</v>
+        <v>42992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126946023</v>
       </c>
       <c r="B2" t="n">
-        <v>42992</v>
+        <v>42998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131092986</v>
       </c>
       <c r="B2" t="n">
-        <v>97880</v>
+        <v>97883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131092986</v>
       </c>
       <c r="B2" t="n">
-        <v>97883</v>
+        <v>97884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131092986</v>
       </c>
       <c r="B2" t="n">
-        <v>97884</v>
+        <v>97886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131092986</v>
       </c>
       <c r="B2" t="n">
-        <v>97886</v>
+        <v>97887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131092986</v>
       </c>
       <c r="B2" t="n">
-        <v>97891</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,58 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126946023</v>
+        <v>131093039</v>
       </c>
       <c r="B3" t="n">
-        <v>42998</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101688</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattunvisslare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrgus alveus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hübner, 1803)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Militärvägen , Upl</t>
+          <t>209, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694575</v>
+        <v>693377</v>
       </c>
       <c r="R3" t="n">
-        <v>6662594</v>
+        <v>6663409</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:25</t>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex födosökande i övergångszonen mellan myr och skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,22 +856,261 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124018489</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gränsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694106</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6662834</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126946023</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43232</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101688</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattunvisslare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrgus alveus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hübner, 1803)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Militärvägen , Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694575</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6662594</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Tomas Johansson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Tomas Johansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17952-2022 artfynd.xlsx
+++ b/artfynd/A 17952-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131093039</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124018489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,8 +1131,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126946023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>